--- a/artfynd/A 54835-2023 artfynd.xlsx
+++ b/artfynd/A 54835-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56219693</v>
       </c>
       <c r="B2" t="n">
-        <v>57304</v>
+        <v>57305</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 54835-2023 artfynd.xlsx
+++ b/artfynd/A 54835-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>56219693</v>
       </c>
       <c r="B2" t="n">
-        <v>57305</v>
+        <v>57306</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 54835-2023 artfynd.xlsx
+++ b/artfynd/A 54835-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,60 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56219693</v>
+        <v>367870</v>
       </c>
       <c r="B2" t="n">
-        <v>57307</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>100856</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102621</v>
+        <v>1256</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Storgröe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Poa remota</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Forselles</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Eriksberg, Gismestad, Ög</t>
+          <t>Hjälmsätter NV, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>527236</v>
+        <v>527370</v>
       </c>
       <c r="R2" t="n">
-        <v>6465125</v>
+        <v>6464949</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,14 +742,24 @@
           <t>Vikingstad</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Arkiv-E-Lin-0028</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1999-01-24</t>
+          <t>1993-06-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1999-01-24</t>
+          <t>1993-06-01</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>20-tal tuvor 107J</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,15 +774,238 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>E-län Floraväktarna</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Via E-län Floraväktarna</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Arkiv Floraväktarlokaler</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>56219693</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57794</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Eriksberg, Gismestad, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>527236</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6465125</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vikingstad</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1999-01-24</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1999-01-24</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Jonas Roth</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Jonas Roth</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>86850996</v>
+      </c>
+      <c r="B4" t="n">
+        <v>111399</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219716</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Krusfrö</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Selinum carvifolia</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Eriksberg 400 m S, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>527401</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6465011</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vikingstad</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-07-13</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-07-13</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Bert Östholm</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Bert Östholm</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54835-2023 artfynd.xlsx
+++ b/artfynd/A 54835-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/367870</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56219693</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1006,8 +1021,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86850996</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>